--- a/design/tables/ShopGoods.xlsx
+++ b/design/tables/ShopGoods.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopGoods" sheetId="1" r:id="R61d6835518024fb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopGoods" sheetId="1" r:id="Rec882ce6343a4906"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -289,6 +289,12 @@
       <x:c r="F1" s="1" t="str">
         <x:v>category</x:v>
       </x:c>
+      <x:c r="G1" t="str">
+        <x:v>demand</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="str">
@@ -307,6 +313,12 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="F2" s="1" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -329,14 +341,38 @@
       <x:c r="F3" s="1" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="G3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="1" t="str"/>
-      <x:c r="B4" s="1" t="str"/>
-      <x:c r="C4" s="1" t="str"/>
-      <x:c r="D4" s="1" t="str"/>
-      <x:c r="E4" s="1" t="str"/>
-      <x:c r="F4" s="1" t="str"/>
+      <x:c r="A4" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>key</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>goodsKey</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="str">
+        <x:v>unlockAfter</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="str">
+        <x:v>price</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>category</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>demand</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -357,6 +393,12 @@
       <x:c r="F5" s="3" t="str">
         <x:v>category</x:v>
       </x:c>
+      <x:c r="G5" t="str">
+        <x:v>demand</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="1" t="n">
@@ -377,6 +419,12 @@
       <x:c r="F6" s="1" t="str">
         <x:v>hot</x:v>
       </x:c>
+      <x:c r="G6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="1" t="n">
@@ -397,6 +445,12 @@
       <x:c r="F7" s="1" t="str">
         <x:v>cold</x:v>
       </x:c>
+      <x:c r="G7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="1" t="n">
@@ -417,6 +471,12 @@
       <x:c r="F8" s="1" t="str">
         <x:v>cold</x:v>
       </x:c>
+      <x:c r="G8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H8" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="1" t="n">
@@ -437,6 +497,12 @@
       <x:c r="F9" s="1" t="str">
         <x:v>hot</x:v>
       </x:c>
+      <x:c r="G9" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H9" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="1" t="n">
@@ -457,6 +523,12 @@
       <x:c r="F10" s="1" t="str">
         <x:v>normal</x:v>
       </x:c>
+      <x:c r="G10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H10" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="1" t="n">
@@ -477,6 +549,12 @@
       <x:c r="F11" s="1" t="str">
         <x:v>normal</x:v>
       </x:c>
+      <x:c r="G11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H11" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="1" t="n">
@@ -497,6 +575,12 @@
       <x:c r="F12" s="1" t="str">
         <x:v>cold</x:v>
       </x:c>
+      <x:c r="G12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H12" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="1" t="n">
@@ -517,6 +601,12 @@
       <x:c r="F13" s="1" t="str">
         <x:v>cold</x:v>
       </x:c>
+      <x:c r="G13" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H13" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="1" t="n">
@@ -536,6 +626,12 @@
       </x:c>
       <x:c r="F14" s="1" t="str">
         <x:v>hot</x:v>
+      </x:c>
+      <x:c r="G14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H14" t="n">
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
